--- a/WorkBot/refactor-experimental/data/orders/Palmer/Palmer_Bakery_20251110.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Palmer/Palmer_Bakery_20251110.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,114 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>98.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>39647</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bindi - Cake Tiramisu Round</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>37.99</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>227.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12569</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>94.98</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>94.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8682</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sweet Street - Pie Caramel Apple Granny Sliced</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>170.98</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>170.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7810</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sweet Street - Pie Oreo Cookie Bash Sliced</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>204.98</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>204.98</t>
         </is>
       </c>
     </row>
